--- a/erp-server/erp-server-bi/src/main/resources/excel/biTargetManagementTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biTargetManagementTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="目标导入" sheetId="1" r:id="rId1"/>
@@ -13,31 +13,283 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数值</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>年份</t>
-  </si>
-  <si>
-    <t>平台</t>
-  </si>
-  <si>
-    <t>品类</t>
-  </si>
-  <si>
-    <t>销量/销售额</t>
-  </si>
-  <si>
-    <t>新品/老品</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>*年份</t>
+  </si>
+  <si>
+    <t>*平台</t>
+  </si>
+  <si>
+    <t>*品类</t>
+  </si>
+  <si>
+    <t>*销量/销售额</t>
+  </si>
+  <si>
+    <t>*新品/老品</t>
   </si>
   <si>
     <t>产品定位</t>
   </si>
   <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>SPU</t>
+    <t>*SKU</t>
+  </si>
+  <si>
+    <t>*SPU</t>
   </si>
   <si>
     <t>品名</t>
@@ -83,12 +335,6 @@
   </si>
   <si>
     <t>错误信息</t>
-  </si>
-  <si>
-    <t>销量</t>
-  </si>
-  <si>
-    <t>新品</t>
   </si>
 </sst>
 </file>
@@ -101,7 +347,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,13 +367,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -275,6 +514,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -597,48 +847,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -648,105 +901,99 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1103,8 +1350,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -1128,105 +1375,91 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:23">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2">
-        <v>2023</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2">
-        <v>12.3</v>
-      </c>
-      <c r="K2">
-        <v>23.65</v>
-      </c>
-      <c r="L2">
-        <v>65.6</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="5">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
+      <formula1>0</formula1>
+      <formula2>2099</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+      <formula1>"销量,销售额"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
+      <formula1>"新品,老品"</formula1>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
       <formula1>0</formula1>
       <formula2>999999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
-      <formula1>0</formula1>
-      <formula2>2099</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:V1048576">
       <formula1>0</formula1>
@@ -1236,5 +1469,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-bi/src/main/resources/excel/biTargetManagementTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biTargetManagementTemplate.xlsx
@@ -266,7 +266,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>*年份</t>
   </si>
@@ -332,9 +332,6 @@
   </si>
   <si>
     <t>十二月</t>
-  </si>
-  <si>
-    <t>错误信息</t>
   </si>
 </sst>
 </file>
@@ -516,12 +513,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1441,18 +1438,20 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="W1" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+      <formula1>"销量,销售额"</formula1>
+    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
       <formula1>0</formula1>
       <formula2>2099</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>"销量,销售额"</formula1>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:V1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>"新品,老品"</formula1>
@@ -1461,10 +1460,6 @@
       <formula1>0</formula1>
       <formula2>999999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:V1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/biTargetManagementTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biTargetManagementTemplate.xlsx
@@ -289,7 +289,7 @@
     <t>*SKU</t>
   </si>
   <si>
-    <t>*SPU</t>
+    <t>SPU</t>
   </si>
   <si>
     <t>品名</t>
@@ -513,12 +513,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1442,16 +1442,12 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>"销量,销售额"</formula1>
-    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
       <formula1>0</formula1>
       <formula2>2099</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:V1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+      <formula1>"销量,销售额"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>"新品,老品"</formula1>
@@ -1460,6 +1456,10 @@
       <formula1>0</formula1>
       <formula2>999999999999999</formula2>
     </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:V1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
